--- a/Chris-Bartosik-projekt-SZABLON.xlsx
+++ b/Chris-Bartosik-projekt-SZABLON.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="111">
   <si>
     <t>Chris Bartosik — szablon jednego projektu</t>
   </si>
@@ -21,31 +21,40 @@
     <t>Jak używać</t>
   </si>
   <si>
-    <t>1. Skopiuj ten plik i nazwij go np. Epic Realty.xlsx (jeden plik = jeden projekt).</t>
-  </si>
-  <si>
-    <t>2. W karcie „Projekt” uzupełnij kolumny EN, PL i ES (jedna tabela).</t>
-  </si>
-  <si>
-    <t>3. Wyślij mi plik albo wrzuć do public/portfolio/{folderName}/.</t>
-  </si>
-  <si>
-    <t>Zasady</t>
-  </si>
-  <si>
-    <t>Theme sekcji jest automatyczne (1=dark, 2=light, 3=muted, potem znowu dark…). Overview zawsze light. Nie wpisujesz theme.</t>
-  </si>
-  <si>
-    <t>Summary / Podsumowanie / Resultado zawsze na końcu — zostaw afterGroup puste. CAPS na stronie robi CSS (label, tytuły, info) — możesz pisać normalnie.</t>
-  </si>
-  <si>
-    <t>Labeli clientLabel / overviewLabel / sections.*.label nie otaczaj nawiasami [ ] — strona dodaje je sama. liveUrl, year, categories, afterGroup tylko w EN.</t>
+    <t>1. Skopiuj plik i nazwij np. Epic Realty.xlsx (jeden Excel = jeden projekt).</t>
+  </si>
+  <si>
+    <t>2. W karcie „Projekt” uzupełnij EN, PL i ES — tylko teksty.</t>
+  </si>
+  <si>
+    <t>3. Wrzuć grafiki do public/portfolio/{folderName}/ (cover, bg, 1.webp, 2.webp…).</t>
+  </si>
+  <si>
+    <t>4. Wyślij mi Excel albo wrzuć go do tego folderu — ja wciągam treści.</t>
+  </si>
+  <si>
+    <t>Co jest automatyczne (nie wpisujesz w Excelu)</t>
+  </si>
+  <si>
+    <t>Zdjęcia i wideo: cover.webp/mp4, bg.webp, 1.webp (overview), 2.webp / 2.1+2.2… — strona czyta je z folderu. Nie ma pól afterGroup / ścieżek grafik.</t>
+  </si>
+  <si>
+    <t>Układ i kolory sekcji: theme idzie automatycznie (dark → light → muted). Overview zawsze jasny. Sekcja Summary / Podsumowanie / Resultado zawsze na końcu.</t>
+  </si>
+  <si>
+    <t>CAPS (etykiety, tytuły, info) robi CSS na stronie — w Excelu pisz normalnie. Nawiasów [ ] przy labelach nie dopisuj.</t>
+  </si>
+  <si>
+    <t>Pola tylko EN (żółte i tak wypełnij w kolumnie EN)</t>
+  </si>
+  <si>
+    <t>slug, folderName, order, comingSoon, categories, year, liveUrl.</t>
   </si>
   <si>
     <t>Sekcja</t>
   </si>
   <si>
-    <t>Klucz (nie zmieniaj)</t>
+    <t>Pole</t>
   </si>
   <si>
     <t>EN</t>
@@ -60,7 +69,7 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>Meta / pliki</t>
+    <t>Start</t>
   </si>
   <si>
     <t>slug</t>
@@ -69,76 +78,46 @@
     <t/>
   </si>
   <si>
-    <t>Nazwa pliku, np. epic-realty → src/content/projects/epic-realty.md</t>
+    <t>Nazwa pliku projektu, np. epic-realty (→ epic-realty.md). Tylko EN.</t>
   </si>
   <si>
     <t>folderName</t>
   </si>
   <si>
-    <t>Folder grafik: public/portfolio/{folderName}/</t>
+    <t>Folder grafik: public/portfolio/{folderName}/. Zdjęcia bierze strona sama. Tylko EN.</t>
   </si>
   <si>
     <t>order</t>
   </si>
   <si>
-    <t>Kolejność na liście (liczba). Mniejsza = wyżej.</t>
+    <t>Kolejność na liście (1, 2, 3…). Mniejsza = wyżej. Tylko EN.</t>
   </si>
   <si>
     <t>comingSoon</t>
   </si>
   <si>
-    <t>true / false</t>
-  </si>
-  <si>
-    <t>thumbnail</t>
-  </si>
-  <si>
-    <t>np. /portfolio/folder/cover.webp lub cover.webm / cover.mp4</t>
-  </si>
-  <si>
-    <t>video</t>
-  </si>
-  <si>
-    <t>Opcjonalne wideo na karcie</t>
-  </si>
-  <si>
-    <t>heroImage</t>
-  </si>
-  <si>
-    <t>Tło hero, np. /portfolio/folder/bg.webp</t>
-  </si>
-  <si>
-    <t>logo</t>
-  </si>
-  <si>
-    <t>Opcjonalnie /logos/….svg</t>
-  </si>
-  <si>
-    <t>overviewGraphic</t>
-  </si>
-  <si>
-    <t>Opcjonalnie — bez tego bierze 1.webp z folderu</t>
-  </si>
-  <si>
-    <t>Karta / Card</t>
+    <t>true = Coming soon (wyszarzone), false = aktywny. Tylko EN.</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t>Filtry strony: ux-ui, motion, ai-engineering, development, branding (po przecinku). Tylko EN.</t>
+  </si>
+  <si>
+    <t>Karta</t>
   </si>
   <si>
     <t>title</t>
   </si>
   <si>
-    <t>Nazwa na liście i stronie. Marki zwykle bez tłumaczenia.</t>
-  </si>
-  <si>
-    <t>tags.0</t>
-  </si>
-  <si>
-    <t>Kategoria pod tytułem na karcie (tłumacz).</t>
-  </si>
-  <si>
-    <t>categories</t>
-  </si>
-  <si>
-    <t>Filtry: ux-ui, motion, ai-engineering, development, branding (po przecinku). Nie tłumacz.</t>
+    <t>Tytuł na liście projektów i w przeglądarce.</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Krótka kategoria pod tytułem (np. Rebranding). Tłumacz w PL/ES jeśli trzeba.</t>
   </si>
   <si>
     <t>Hero</t>
@@ -147,28 +126,28 @@
     <t>client</t>
   </si>
   <si>
-    <t>Nazwa klienta. Zwykle bez tłumaczenia. Na stronie i tak CAPS.</t>
+    <t>Nazwa klienta. Zwykle bez tłumaczenia.</t>
   </si>
   <si>
     <t>clientLabel</t>
   </si>
   <si>
-    <t>Tekst w [ … ] — wpisz bez nawiasów, np. Client. Puste = domyślne UI.</t>
+    <t>Etykieta nad klientem, bez [ ]. Puste = domyślne Client / Klient / Cliente.</t>
   </si>
   <si>
     <t>heroSubtitle</t>
   </si>
   <si>
-    <t>Zachowaj łamanie linii (Enter = nowa linia na stronie).</t>
-  </si>
-  <si>
-    <t>Info row</t>
+    <t>Podtytuł pod klientem. Enter = nowa linia na stronie.</t>
+  </si>
+  <si>
+    <t>Info</t>
   </si>
   <si>
     <t>service</t>
   </si>
   <si>
-    <t>Puste = ukryte. Na stronie CAPS.</t>
+    <t>Puste = ukryte na stronie.</t>
   </si>
   <si>
     <t>industry</t>
@@ -183,7 +162,7 @@
     <t>year</t>
   </si>
   <si>
-    <t>Rok, np. 2025. Nie tłumacz.</t>
+    <t>Rok, np. 2025. Tylko EN.</t>
   </si>
   <si>
     <t>Live</t>
@@ -192,34 +171,34 @@
     <t>liveLabel</t>
   </si>
   <si>
-    <t>Podkreślony napis linku. Tłumacz.</t>
+    <t>Tekst linku (jeśli jest live). Puste = bez linku.</t>
   </si>
   <si>
     <t>liveUrl</t>
   </si>
   <si>
-    <t>URL — tylko EN, bez tłumaczenia.</t>
-  </si>
-  <si>
-    <t>Overview / Kontekst</t>
+    <t>Adres URL. Tylko EN. Puste = bez linku.</t>
+  </si>
+  <si>
+    <t>Overview</t>
   </si>
   <si>
     <t>overviewLabel</t>
   </si>
   <si>
-    <t>Tekst w [ … ] bez nawiasów. Puste = Overview/Kontekst/Descripción. Overview zawsze light.</t>
+    <t>Etykieta bez [ ]. Puste = Overview / Kontekst / Descripción.</t>
   </si>
   <si>
     <t>overviewTitle</t>
   </si>
   <si>
-    <t>Nagłówek. Na stronie CAPS.</t>
+    <t>Nagłówek bloku overview.</t>
   </si>
   <si>
     <t>overviewText</t>
   </si>
   <si>
-    <t>Treść. Puste linie = nowe akapity. Bez CAPS.</t>
+    <t>Treść. Pusta linia = nowy akapit.</t>
   </si>
   <si>
     <t>Sekcja 01</t>
@@ -228,22 +207,19 @@
     <t>sections.0.label</t>
   </si>
   <si>
-    <t>Bez [ ]. Na stronie CAPS. Theme auto: dark. Summary = zawsze ostatnia (bez afterGroup).</t>
+    <t>Etykieta bez [ ], np. Challenge / Wyzwanie. Puste = sekcja nieużywana.</t>
   </si>
   <si>
     <t>sections.0.title</t>
   </si>
   <si>
+    <t>Nagłówek sekcji.</t>
+  </si>
+  <si>
     <t>sections.0.text</t>
   </si>
   <si>
-    <t>Treść. Listy: - **Tytuł**: opis. Bez CAPS.</t>
-  </si>
-  <si>
-    <t>sections.0.afterGroup</t>
-  </si>
-  <si>
-    <t>Tylko EN. Po której grupie galerii wstawić (np. 2 = po 2.webp). Puste = na końcu. Summary zostaw puste.</t>
+    <t>Treść. Listy: - **Tytuł**: opis. Puste = sekcja nieużywana.</t>
   </si>
   <si>
     <t>Sekcja 02</t>
@@ -252,36 +228,24 @@
     <t>sections.1.label</t>
   </si>
   <si>
-    <t>Bez [ ]. Na stronie CAPS. Theme auto: light. Summary = zawsze ostatnia (bez afterGroup).</t>
-  </si>
-  <si>
     <t>sections.1.title</t>
   </si>
   <si>
     <t>sections.1.text</t>
   </si>
   <si>
-    <t>sections.1.afterGroup</t>
-  </si>
-  <si>
     <t>Sekcja 03</t>
   </si>
   <si>
     <t>sections.2.label</t>
   </si>
   <si>
-    <t>Bez [ ]. Na stronie CAPS. Theme auto: muted. Summary = zawsze ostatnia (bez afterGroup).</t>
-  </si>
-  <si>
     <t>sections.2.title</t>
   </si>
   <si>
     <t>sections.2.text</t>
   </si>
   <si>
-    <t>sections.2.afterGroup</t>
-  </si>
-  <si>
     <t>Sekcja 04</t>
   </si>
   <si>
@@ -294,9 +258,6 @@
     <t>sections.3.text</t>
   </si>
   <si>
-    <t>sections.3.afterGroup</t>
-  </si>
-  <si>
     <t>Sekcja 05</t>
   </si>
   <si>
@@ -309,9 +270,6 @@
     <t>sections.4.text</t>
   </si>
   <si>
-    <t>sections.4.afterGroup</t>
-  </si>
-  <si>
     <t>Sekcja 06</t>
   </si>
   <si>
@@ -324,9 +282,6 @@
     <t>sections.5.text</t>
   </si>
   <si>
-    <t>sections.5.afterGroup</t>
-  </si>
-  <si>
     <t>Sekcja 07</t>
   </si>
   <si>
@@ -339,9 +294,6 @@
     <t>sections.6.text</t>
   </si>
   <si>
-    <t>sections.6.afterGroup</t>
-  </si>
-  <si>
     <t>Sekcja 08</t>
   </si>
   <si>
@@ -354,31 +306,46 @@
     <t>sections.7.text</t>
   </si>
   <si>
-    <t>sections.7.afterGroup</t>
-  </si>
-  <si>
-    <t>Plik w public/portfolio/{folderName}/</t>
-  </si>
-  <si>
-    <t>Notatka</t>
+    <t>Wrzucasz do folderu projektu</t>
+  </si>
+  <si>
+    <t>Co robi</t>
   </si>
   <si>
     <t>cover.webp / cover.webm / cover.mp4</t>
   </si>
   <si>
-    <t>bg.webp (hero)</t>
-  </si>
-  <si>
-    <t>1.webp (overview)</t>
-  </si>
-  <si>
-    <t>2.webp, 3.webp… (full)</t>
-  </si>
-  <si>
-    <t>2.1 + 2.2, 3.1 + 3.2… (pary)</t>
-  </si>
-  <si>
-    <t>ten Excel w folderze (opcjonalnie)</t>
+    <t>Okładka na liście projektów</t>
+  </si>
+  <si>
+    <t>bg.webp</t>
+  </si>
+  <si>
+    <t>Tło hero na stronie projektu</t>
+  </si>
+  <si>
+    <t>1.webp</t>
+  </si>
+  <si>
+    <t>Grafika przy Overview (opcjonalnie)</t>
+  </si>
+  <si>
+    <t>2.webp, 3.webp, 4.webp…</t>
+  </si>
+  <si>
+    <t>Pełne kadry w galerii (kolejność = numer)</t>
+  </si>
+  <si>
+    <t>2.1.webp + 2.2.webp…</t>
+  </si>
+  <si>
+    <t>Pary pod pełnym kadrem o tym samym numerze</t>
+  </si>
+  <si>
+    <t>ten Excel (opcjonalnie)</t>
+  </si>
+  <si>
+    <t>Żebym mógł wciągnąć teksty z folderu</t>
   </si>
 </sst>
 </file>
@@ -430,12 +397,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F7F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -473,7 +440,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -829,39 +795,54 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="7" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -872,213 +853,213 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="5" width="56" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="6" max="6" width="52" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1086,259 +1067,259 @@
         <v>35</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1346,59 +1327,59 @@
         <v>62</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1406,79 +1387,79 @@
         <v>69</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="B30" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1489,16 +1470,16 @@
         <v>78</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1506,179 +1487,179 @@
         <v>77</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="5" t="s">
+      <c r="C36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="B37" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="5" t="s">
+      <c r="C37" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1686,363 +1667,103 @@
         <v>89</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>95</v>
-      </c>
       <c r="C43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F58"/>
+  <autoFilter ref="A1:F45"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2053,63 +1774,64 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>17</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Chris-Bartosik-projekt-SZABLON.xlsx
+++ b/Chris-Bartosik-projekt-SZABLON.xlsx
@@ -219,7 +219,7 @@
     <t>sections.0.text</t>
   </si>
   <si>
-    <t>Treść. Listy: - **Tytuł**: opis. Puste = sekcja nieużywana.</t>
+    <t>Treść. Pusta linia = nowy akapit. Puste pole = sekcja nieużywana.</t>
   </si>
   <si>
     <t>Sekcja 02</t>
